--- a/Unity/Assets/Config/Excel/MonsterBatchConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterBatchConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="22185" windowHeight="9555"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,21 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
   <si>
     <t>##var</t>
   </si>
   <si>
     <t>Id</t>
-  </si>
-  <si>
-    <t>DelayTime</t>
-  </si>
-  <si>
-    <t>SpawnInterval</t>
-  </si>
-  <si>
-    <t>SpawnNum</t>
   </si>
   <si>
     <t>SpawnPosition</t>
@@ -56,22 +47,10 @@
     <t>int</t>
   </si>
   <si>
-    <t>float</t>
-  </si>
-  <si>
     <t>vector2</t>
   </si>
   <si>
     <t>##</t>
-  </si>
-  <si>
-    <t>延迟出现时间</t>
-  </si>
-  <si>
-    <t>刷新间隔</t>
-  </si>
-  <si>
-    <t>生成几次</t>
   </si>
   <si>
     <t>刷新位置</t>
@@ -1113,14 +1092,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelCol="6"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1133,179 +1112,98 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:4">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="D2" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:7">
-      <c r="A2" s="1" t="s">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:4">
+      <c r="A3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:7">
+    <row r="4" customHeight="1" spans="2:4">
       <c r="B4" s="2">
         <v>1010101</v>
       </c>
-      <c r="C4" s="2">
-        <v>1</v>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="D4" s="2">
-        <v>2</v>
-      </c>
-      <c r="E4" s="2">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="2">
         <v>10000001</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:7">
+    <row r="5" customHeight="1" spans="2:4">
       <c r="B5" s="2">
         <v>1010201</v>
       </c>
-      <c r="C5" s="2">
-        <v>1</v>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="D5" s="2">
-        <v>2</v>
-      </c>
-      <c r="E5" s="2">
-        <v>2</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="2">
         <v>10000001</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:7">
+    <row r="6" customHeight="1" spans="2:4">
       <c r="B6" s="2">
         <v>1010202</v>
       </c>
-      <c r="C6" s="2">
-        <v>1</v>
+      <c r="C6" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="D6" s="2">
-        <v>2</v>
-      </c>
-      <c r="E6" s="2">
-        <v>2</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="2">
         <v>10000002</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="2:7">
+    <row r="7" customHeight="1" spans="2:4">
       <c r="B7" s="2">
         <v>1010301</v>
       </c>
-      <c r="C7" s="2">
-        <v>1</v>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="D7" s="2">
-        <v>2</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="2">
         <v>10000003</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="2:7">
+    <row r="8" customHeight="1" spans="2:4">
       <c r="B8" s="2">
         <v>2010101</v>
       </c>
-      <c r="C8" s="2">
-        <v>1</v>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="D8" s="2">
-        <v>2</v>
-      </c>
-      <c r="E8" s="2">
-        <v>2</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="2">
         <v>10000001</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="2:7">
+    <row r="9" customHeight="1" spans="2:4">
       <c r="B9" s="2">
         <v>2010201</v>
       </c>
-      <c r="C9" s="2">
-        <v>1</v>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="D9" s="2">
-        <v>2</v>
-      </c>
-      <c r="E9" s="2">
-        <v>2</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="2">
         <v>10000001</v>
       </c>
     </row>

--- a/Unity/Assets/Config/Excel/MonsterBatchConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterBatchConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>##var</t>
   </si>
@@ -35,6 +35,9 @@
     <t>Id</t>
   </si>
   <si>
+    <t>SpawnTime</t>
+  </si>
+  <si>
     <t>SpawnPosition</t>
   </si>
   <si>
@@ -47,10 +50,16 @@
     <t>int</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>vector2</t>
   </si>
   <si>
     <t>##</t>
+  </si>
+  <si>
+    <t>刷新时间</t>
   </si>
   <si>
     <t>刷新位置</t>
@@ -1092,14 +1101,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelCol="3"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:4">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1112,98 +1121,125 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:4">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>5</v>
-      </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:4">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:4">
+    <row r="4" customHeight="1" spans="2:5">
       <c r="B4" s="2">
         <v>1010101</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2">
+      <c r="C4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2">
         <v>10000001</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:4">
+    <row r="5" customHeight="1" spans="2:5">
       <c r="B5" s="2">
         <v>1010201</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="C5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2">
         <v>10000001</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:4">
+    <row r="6" customHeight="1" spans="2:5">
       <c r="B6" s="2">
         <v>1010202</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="2">
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2">
         <v>10000002</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="2:4">
+    <row r="7" customHeight="1" spans="2:5">
       <c r="B7" s="2">
         <v>1010301</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="C7" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="2">
         <v>10000003</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="2:4">
+    <row r="8" customHeight="1" spans="2:5">
       <c r="B8" s="2">
         <v>2010101</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="2">
+      <c r="C8" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="2">
         <v>10000001</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="2:4">
+    <row r="9" customHeight="1" spans="2:5">
       <c r="B9" s="2">
         <v>2010201</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="2">
+      <c r="C9" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="2">
         <v>10000001</v>
       </c>
     </row>

--- a/Unity/Assets/Config/Excel/MonsterBatchConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterBatchConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
   <si>
     <t>##var</t>
   </si>
@@ -59,16 +59,19 @@
     <t>##</t>
   </si>
   <si>
-    <t>刷新时间</t>
-  </si>
-  <si>
-    <t>刷新位置</t>
+    <t>生成时间</t>
+  </si>
+  <si>
+    <t>生成位置</t>
   </si>
   <si>
     <t>怪物Id</t>
   </si>
   <si>
     <t>0,5</t>
+  </si>
+  <si>
+    <t>1,5</t>
   </si>
   <si>
     <t>5,5</t>
@@ -1101,7 +1104,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
@@ -1175,13 +1178,13 @@
     </row>
     <row r="5" customHeight="1" spans="2:5">
       <c r="B5" s="2">
-        <v>1010201</v>
+        <v>1010102</v>
       </c>
       <c r="C5" s="2">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2">
         <v>10000001</v>
@@ -1189,35 +1192,35 @@
     </row>
     <row r="6" customHeight="1" spans="2:5">
       <c r="B6" s="2">
-        <v>1010202</v>
+        <v>1010201</v>
       </c>
       <c r="C6" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" s="2">
-        <v>10000002</v>
+        <v>10000001</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="2:5">
       <c r="B7" s="2">
-        <v>1010301</v>
+        <v>1010202</v>
       </c>
       <c r="C7" s="2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2">
-        <v>10000003</v>
+        <v>10000002</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="2:5">
       <c r="B8" s="2">
-        <v>2010101</v>
+        <v>1010301</v>
       </c>
       <c r="C8" s="2">
         <v>0.5</v>
@@ -1226,12 +1229,12 @@
         <v>13</v>
       </c>
       <c r="E8" s="2">
-        <v>10000001</v>
+        <v>10000003</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="2:5">
       <c r="B9" s="2">
-        <v>2010201</v>
+        <v>2010101</v>
       </c>
       <c r="C9" s="2">
         <v>0.5</v>
@@ -1240,6 +1243,20 @@
         <v>13</v>
       </c>
       <c r="E9" s="2">
+        <v>10000001</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="2:5">
+      <c r="B10" s="2">
+        <v>2010201</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="2">
         <v>10000001</v>
       </c>
     </row>

--- a/Unity/Assets/Config/Excel/MonsterBatchConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterBatchConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22185" windowHeight="9555"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -68,13 +68,13 @@
     <t>怪物Id</t>
   </si>
   <si>
+    <t>-5,5</t>
+  </si>
+  <si>
+    <t>5,5</t>
+  </si>
+  <si>
     <t>0,5</t>
-  </si>
-  <si>
-    <t>1,5</t>
-  </si>
-  <si>
-    <t>5,5</t>
   </si>
 </sst>
 </file>
@@ -765,7 +765,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -775,13 +775,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1108,23 +1117,25 @@
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="17.875" style="2"/>
+    <col min="2" max="3" width="17.875" style="2"/>
+    <col min="4" max="4" width="17.875" style="3"/>
+    <col min="5" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1132,16 +1143,16 @@
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1149,16 +1160,16 @@
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1169,7 +1180,7 @@
       <c r="C4" s="2">
         <v>0.5</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="2">
@@ -1183,7 +1194,7 @@
       <c r="C5" s="2">
         <v>0.2</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="2">
@@ -1197,8 +1208,8 @@
       <c r="C6" s="2">
         <v>0.5</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>13</v>
+      <c r="D6" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="E6" s="2">
         <v>10000001</v>
@@ -1211,8 +1222,8 @@
       <c r="C7" s="2">
         <v>1</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>15</v>
+      <c r="D7" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="E7" s="2">
         <v>10000002</v>
@@ -1225,8 +1236,8 @@
       <c r="C8" s="2">
         <v>0.5</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>13</v>
+      <c r="D8" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="E8" s="2">
         <v>10000003</v>
@@ -1239,8 +1250,8 @@
       <c r="C9" s="2">
         <v>0.5</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>13</v>
+      <c r="D9" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="E9" s="2">
         <v>10000001</v>
@@ -1253,8 +1264,8 @@
       <c r="C10" s="2">
         <v>0.5</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>13</v>
+      <c r="D10" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="E10" s="2">
         <v>10000001</v>

--- a/Unity/Assets/Config/Excel/MonsterBatchConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterBatchConfig.xlsx
@@ -1198,7 +1198,7 @@
         <v>14</v>
       </c>
       <c r="E5" s="2">
-        <v>10000001</v>
+        <v>10000002</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="2:5">
